--- a/测试/恒流源测试/测试记录与分析/测试数据02.xlsx
+++ b/测试/恒流源测试/测试记录与分析/测试数据02.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WechatFiles\xwechat_files\wxid_g1fxils7md0q12_66bb\msg\file\2026-06\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS\University\电赛\26校内赛\NC-Current-Source\测试\恒流源测试\测试记录与分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168933D8-6018-4EBC-AB48-AC586781B1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28781B9A-58DA-44A0-8FB7-31D499576A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新建 XLS 工作表" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>DAC2_mea_mV</t>
   </si>
@@ -642,14 +645,22 @@
     <t>deltaI</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>Rload=28.6</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>deltaI(Imeas-Idisp)_mA</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0.000_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -728,13 +739,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -1392,7 +1403,1230 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.899759405074366E-2"/>
+          <c:y val="0.19486111111111112"/>
+          <c:w val="0.88389129483814521"/>
+          <c:h val="0.72088764946048411"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[1]Sheet3!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>deltaI(Imeas-Idisp)_mA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]Sheet3!$F$2:$F$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]Sheet3!$G$2:$G$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.70899999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-86F1-4C3F-866E-89F54C0D2E27}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1561046976"/>
+        <c:axId val="1561047392"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1561046976"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1561047392"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1561047392"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1561046976"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]Sheet3!$F$6:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]Sheet3!$G$6:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-31E0-42F7-B1DF-60A22B3595AB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2043023952"/>
+        <c:axId val="2043024784"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2043023952"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2043024784"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2043024784"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2043023952"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.13450962379702538"/>
+                  <c:y val="-0.18067949839603384"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="zh-CN"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>[1]Sheet3!$F$8:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>[1]Sheet3!$G$8:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.62</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F8D3-4CDC-87E8-C82F4FD98E03}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2045167248"/>
+        <c:axId val="2045166832"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2045167248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2045166832"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2045166832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2045167248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1948,20 +3182,1568 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>6488</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>144117</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>275142</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>34213</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>309079</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>43622</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>577733</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>116892</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1986,7 +4768,218 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>461131</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>22678</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>150203</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>41604</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EB20206-1DC3-40BC-B045-DBDFDA16F786}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>587963</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>59799</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>283754</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>154499</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="图表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD9CBD8F-6AB4-4FDA-8401-DE8A7A667E93}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>329789</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>82314</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>607601</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>148706</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="图表 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14D919CA-977F-4CB5-A017-20A281596D62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="新建 XLS 工作表"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="1">
+          <cell r="G1" t="str">
+            <v>deltaI(Imeas-Idisp)_mA</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="F2">
+            <v>10</v>
+          </cell>
+          <cell r="G2">
+            <v>0.56999999999999995</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="F3">
+            <v>20</v>
+          </cell>
+          <cell r="G3">
+            <v>0.70899999999999996</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4">
+            <v>30</v>
+          </cell>
+          <cell r="G4">
+            <v>0.79</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6">
+            <v>50</v>
+          </cell>
+          <cell r="G6">
+            <v>0.68</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7">
+            <v>60</v>
+          </cell>
+          <cell r="G7">
+            <v>0.32</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8">
+            <v>70</v>
+          </cell>
+          <cell r="G8">
+            <v>0.17</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9">
+            <v>80</v>
+          </cell>
+          <cell r="G9">
+            <v>0.31</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10">
+            <v>90</v>
+          </cell>
+          <cell r="G10">
+            <v>0.9</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11">
+            <v>100</v>
+          </cell>
+          <cell r="G11">
+            <v>0.62</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3061,74 +6054,153 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED2F4223-4ECA-4AD7-AFC2-E15C0394F899}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.08984375" customWidth="1"/>
+    <col min="7" max="7" width="27.453125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>18</v>
       </c>
+      <c r="E1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3">
+        <v>0.70899999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <v>30</v>
+      </c>
+      <c r="G4">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>-3.7</v>
       </c>
       <c r="B5">
         <v>450</v>
       </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>0.47</v>
+      </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>-2.5</v>
       </c>
       <c r="B6">
         <v>400</v>
       </c>
+      <c r="F6">
+        <v>50</v>
+      </c>
+      <c r="G6">
+        <v>0.68</v>
+      </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>-1.5</v>
       </c>
       <c r="B7">
         <v>350</v>
       </c>
+      <c r="F7">
+        <v>60</v>
+      </c>
+      <c r="G7">
+        <v>0.32</v>
+      </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>-0.3</v>
       </c>
       <c r="B8">
         <v>300</v>
       </c>
+      <c r="F8">
+        <v>70</v>
+      </c>
+      <c r="G8">
+        <v>0.17</v>
+      </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.9</v>
       </c>
       <c r="B9">
         <v>250</v>
       </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9">
+        <v>0.31</v>
+      </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1.7</v>
       </c>
       <c r="B10">
         <v>200</v>
       </c>
+      <c r="F10">
+        <v>90</v>
+      </c>
+      <c r="G10">
+        <v>0.9</v>
+      </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
       <c r="B11">
         <v>150</v>
       </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>0.62</v>
+      </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -3136,7 +6208,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3.1</v>
       </c>
@@ -3144,7 +6216,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2.8</v>
       </c>
@@ -3152,7 +6224,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3.5</v>
       </c>

--- a/测试/恒流源测试/测试记录与分析/测试数据02.xlsx
+++ b/测试/恒流源测试/测试记录与分析/测试数据02.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IRIS\University\电赛\26校内赛\NC-Current-Source\测试\恒流源测试\测试记录与分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28781B9A-58DA-44A0-8FB7-31D499576A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0D9C44-4BBC-453F-9050-5463737CE34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新建 XLS 工作表" sheetId="1" r:id="rId1"/>
